--- a/02_加值成品/生物/生物1-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物1-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物1-2 細胞的構造與功能　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國一(七年級) 生物1-2 細胞的構造與功能　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>生物構造與功能的基本單位是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>顯微鏡</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>細胞膜質核</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>細胞</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>植物細胞</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>基本</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>控制物質進出的是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>細胞</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>目鏡×物鏡</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>細胞膜</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>細胞膜質核</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>進出</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>細胞的控制中心是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>目鏡×物鏡</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>細胞核</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>玻片標本</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>控制</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>植物細胞特有的堅硬構造是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>目鏡×物鏡</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>細胞膜</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>細胞壁</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>生命活動</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>支持</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>植物行光合作用的胞器是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>葉綠體</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>細胞壁</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>光合作用</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>細胞質</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>光合</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>觀察細胞用什麼儀器？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>植物細胞</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>支持與保護</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>顯微鏡</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>細胞膜</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>放大</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>進行代謝反應的是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>生命活動</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>光合作用</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>細胞質</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>目鏡×物鏡</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>代謝</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>動物細胞有細胞壁嗎？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>沒有</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>支持與保護</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>顯微鏡</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>細胞膜</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>植物才有</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>生物體由一個或多個什麼組成？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>細胞質</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>顯微鏡</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>細胞</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>葉綠體</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>組成</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>植物細胞儲水的大構造是？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>光合作用</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>大液泡</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>細胞</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>葉綠體</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>液泡</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物1-2 細胞的構造與功能　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國一(七年級) 生物1-2 細胞的構造與功能　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>動植物細胞共有構造？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>目鏡×物鏡</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>玻片標本</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>細胞膜質核</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>葉綠體</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>共有</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>大液泡是哪種細胞特有？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>大液泡</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>光合作用</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>葉綠體</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>植物細胞</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>儲存</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>葉綠體的功能是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>光合作用</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>顯微鏡</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>目鏡×物鏡</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>細胞核</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>製養分</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>細胞壁的功能是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>支持與保護</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>生命活動</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>細胞質</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>細胞膜質核</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>支撐</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>細胞核控制細胞的？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>細胞核</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>細胞質</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>光合作用</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>生命活動</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>顯微鏡觀察需製作？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>大液泡</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>支持與保護</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>細胞核</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>玻片標本</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>標本</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>紅血球沒有的是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>細胞分裂補充新細胞</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>便於顯微鏡觀察</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>見細胞壁與葉綠體</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>細胞核(成熟後)</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>特例</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>細胞學說指細胞來自？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>顯微鏡</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>目鏡×物鏡</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>細胞壁</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>細胞</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>分裂</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>顯微鏡總放大倍率如何計算？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>植物細胞</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>細胞核</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>細胞壁</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>目鏡×物鏡</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>倍率</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>製作玻片標本的目的是？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>便於顯微鏡觀察</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>儲存並維持膨壓支撐</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>含遺傳物質調控細胞活動</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>縮小使細胞失去膨壓</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>標本</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物1-2 細胞的構造與功能　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國一(七年級) 生物1-2 細胞的構造與功能　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>如何從構造分辨動物與植物細胞？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>含遺傳物質調控細胞活動</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>細胞分裂補充新細胞</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>膜控制進出、壁支持保護</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>植物有細胞壁葉綠體大液泡</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>區分</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>細胞膜與細胞壁功能差異？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>含色素捕捉光能行光合</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>便於顯微鏡觀察</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>膜控制進出、壁支持保護</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>細胞分裂補充新細胞</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>區別</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>葉綠體構造與其功能如何配合？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>植物有細胞壁葉綠體大液泡</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>縮小使細胞失去膨壓</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>膜控制進出、壁支持保護</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>含色素捕捉光能行光合</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>配合</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>細胞核為何稱控制中心？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>含遺傳物質調控細胞活動</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>植物有細胞壁葉綠體大液泡</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>膜控制進出、壁支持保護</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>細胞分裂補充新細胞</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>核</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>為何生物體受傷能修復？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>細胞核(成熟後)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>含色素捕捉光能行光合</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>細胞分裂補充新細胞</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>縮小使細胞失去膨壓</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>分裂</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>顯微鏡下如何辨識植物細胞？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>見細胞壁與葉綠體</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>膜控制進出、壁支持保護</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>含遺傳物質調控細胞活動</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>便於顯微鏡觀察</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>觀察</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>細胞學說對生物學的意義？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>奠定生物由細胞組成的基礎</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>含遺傳物質調控細胞活動</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>利於物質快速進出交換</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>含色素捕捉光能行光合</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>意義</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>大液泡對植物細胞的作用？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>儲存並維持膨壓支撐</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>細胞分裂補充新細胞</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>便於顯微鏡觀察</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>膜控制進出、壁支持保護</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>液泡</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何多數細胞體積都很小？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>奠定生物由細胞組成的基礎</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>便於顯微鏡觀察</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>利於物質快速進出交換</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>縮小使細胞失去膨壓</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>大小</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>植物細胞失水時大液泡會如何？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>細胞核(成熟後)</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>便於顯微鏡觀察</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>縮小使細胞失去膨壓</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>見細胞壁與葉綠體</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>液泡</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/生物/生物1-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物1-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>基本</t>
+          <t>基本單位：細胞是所有生物體構造與功能最小的組成單位，這就是細胞學說的重要概念</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>進出</t>
+          <t>控制進出：細胞膜包在細胞最外層，負責管理養分與廢物進出細胞</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>控制</t>
+          <t>控制中心：細胞核裡含有遺傳物質，能指揮並調控整個細胞的各種活動</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>支持</t>
+          <t>支持保護：細胞壁在細胞膜外圍，質地堅硬，能支撐並保護植物細胞</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>光合</t>
+          <t>行光合作用：葉綠體含有葉綠素，能利用光能製造養分，是植物細胞特有的胞器</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>放大</t>
+          <t>放大觀察：細胞非常微小，肉眼看不到，需要用顯微鏡放大才能觀察清楚</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>代謝</t>
+          <t>進行代謝：細胞質是細胞膜內、細胞核外的膠狀物質，許多化學反應在這裡進行</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>植物才有</t>
+          <t>植物才有：細胞壁是植物細胞特有的構造，動物細胞沒有這個構造</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>組成</t>
+          <t>組成：所有生物體都是由一個或多個細胞所構成的，細胞是生物體最基本的構造單位</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>液泡</t>
+          <t>液泡：植物細胞內有一個很大的液泡，能儲存水分和養分，並幫助維持細胞的形狀</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>共有</t>
+          <t>共同構造：不論動物或植物細胞，都具有細胞膜、細胞質與細胞核這三種構造</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>儲存</t>
+          <t>儲存構造：大液泡能儲存水分與養分，是植物細胞特有、動物細胞沒有的構造</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>製養分</t>
+          <t>製造養分：葉綠體能利用光能，把二氧化碳和水轉變成葡萄糖等養分</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>支撐</t>
+          <t>支撐保護：細胞壁質地堅硬，能讓植物細胞維持固定形狀並抵抗外力</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>調控中心：細胞核內的遺傳物質能指揮細胞進行生長、分裂等各種生命活動</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>標本</t>
+          <t>製作標本：要用顯微鏡觀察細胞，需先把材料處理成薄薄的玻片標本</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>特例</t>
+          <t>特殊例子：人類成熟的紅血球會失去細胞核，這是少數沒有細胞核的細胞</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>分裂</t>
+          <t>細胞分裂：細胞學說認為新細胞都是由原本存在的細胞分裂產生的</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>倍率</t>
+          <t>倍率：顯微鏡的總放大倍率＝目鏡倍率乘以物鏡倍率，例如目鏡10倍、物鏡40倍，總倍率就是400倍</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>標本</t>
+          <t>標本：把樣本製成薄薄的玻片標本，可以讓光線穿透樣本，方便放在顯微鏡下觀察內部構造</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>區分</t>
+          <t>構造比對：只要看到細胞壁、葉綠體或大液泡，就能判斷這是植物細胞</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>區別</t>
+          <t>功能不同：細胞膜負責控制物質進出，細胞壁則負責支撐與保護整個細胞</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>配合</t>
+          <t>構造配合功能：葉綠體含有能吸收光能的色素，才能進行光合作用製造養分</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>核</t>
+          <t>含遺傳物質：細胞核裡儲存著遺傳物質，能指揮並調控細胞所有的生命活動</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>分裂</t>
+          <t>細胞分裂修補：受傷部位的細胞會不斷分裂，產生新細胞來修補受損組織</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>觀察</t>
+          <t>觀察特徵：在顯微鏡下若看到規則的細胞壁與綠色的葉綠體，就是植物細胞</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>意義</t>
+          <t>重要基礎：細胞學說說明所有生物都由細胞組成，是生物學的重要基礎理論</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>液泡</t>
+          <t>儲存支撐：大液泡儲存水分和養分，並能撐起細胞讓植物保持挺立</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>大小</t>
+          <t>大小：細胞越小，表面積相對於體積的比例越大，養分、氧氣等物質才能更快速地進出細胞、完成交換，所以大多數細胞體積都很小</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>液泡</t>
+          <t>液泡：植物細胞缺水時，液泡裡的水分減少而縮小，細胞失去原本撐起來的膨壓，看起來就會枯萎軟垂</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/生物/生物1-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物1-2_三種難度測驗卷.xlsx
@@ -563,12 +563,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>顯微鏡</t>
+          <t>葉綠體</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>細胞膜質核</t>
+          <t>目鏡×物鏡</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>植物細胞</t>
+          <t>大液泡</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -603,22 +603,22 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>細胞</t>
+          <t>葉綠體</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>大液泡</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>細胞膜</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
           <t>目鏡×物鏡</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>細胞膜</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>細胞膜質核</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>目鏡×物鏡</t>
+          <t>細胞膜質核</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>沒有</t>
+          <t>細胞壁</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>玻片標本</t>
+          <t>支持與保護</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>目鏡×物鏡</t>
+          <t>沒有</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>細胞膜</t>
+          <t>葉綠體</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>生命活動</t>
+          <t>細胞質</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>生命活動</t>
+          <t>顯微鏡</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>目鏡×物鏡</t>
+          <t>葉綠體</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>細胞質</t>
+          <t>大液泡</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>顯微鏡</t>
+          <t>目鏡×物鏡</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>葉綠體</t>
+          <t>光合作用</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>目鏡×物鏡</t>
+          <t>顯微鏡</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>玻片標本</t>
+          <t>葉綠體</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>葉綠體</t>
+          <t>支持與保護</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>大液泡</t>
+          <t>生命活動</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>光合作用</t>
+          <t>細胞質</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -1319,17 +1319,17 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>顯微鏡</t>
+          <t>葉綠體</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>目鏡×物鏡</t>
+          <t>光合作用</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>細胞壁</t>
+          <t>生命活動</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
